--- a/품목일괄등록양식.xlsx
+++ b/품목일괄등록양식.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6FB8BE9-541A-4CAF-A3E4-3F615D78B6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57570EFE-5DD2-4CAC-B61F-5F5DC0CAAE91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1188,7 +1188,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="525">
   <si>
     <t>* 품목코드</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -2767,9 +2767,6 @@
   <si>
     <t>09M325039A</t>
     <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>면세</t>
   </si>
   <si>
     <t>1000000</t>
@@ -3934,10 +3931,10 @@
         <v>26</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="12">
@@ -3950,16 +3947,16 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="12">
@@ -3978,10 +3975,10 @@
         <v>27</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G4" s="12">
         <v>550000</v>
@@ -3996,16 +3993,16 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="11" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G5" s="12"/>
       <c r="H5" s="12">
@@ -4024,10 +4021,10 @@
         <v>29</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="12">
@@ -4046,10 +4043,10 @@
         <v>30</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G7" s="12">
         <v>340000</v>
@@ -4070,10 +4067,10 @@
         <v>31</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G8" s="12"/>
       <c r="H8" s="12">
@@ -4092,10 +4089,10 @@
         <v>32</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="12">
@@ -4114,10 +4111,10 @@
         <v>33</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G10" s="12"/>
       <c r="H10" s="12">
@@ -4136,10 +4133,10 @@
         <v>34</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G11" s="12">
         <v>330000</v>
@@ -4160,10 +4157,10 @@
         <v>35</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G12" s="12"/>
       <c r="H12" s="12">
@@ -4182,10 +4179,10 @@
         <v>36</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G13" s="12"/>
       <c r="H13" s="12">
@@ -4204,10 +4201,10 @@
         <v>37</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G14" s="12"/>
       <c r="H14" s="12">
@@ -4220,16 +4217,16 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G15" s="12"/>
       <c r="H15" s="12">
@@ -4248,10 +4245,10 @@
         <v>38</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G16" s="12"/>
       <c r="H16" s="12">
@@ -4270,10 +4267,10 @@
         <v>39</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G17" s="12"/>
       <c r="H17" s="12">
@@ -4292,10 +4289,10 @@
         <v>40</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G18" s="12"/>
       <c r="H18" s="12">
@@ -4314,10 +4311,10 @@
         <v>40</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G19" s="12"/>
       <c r="H19" s="12">
@@ -4336,10 +4333,10 @@
         <v>41</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G20" s="12"/>
       <c r="H20" s="12">
@@ -4358,10 +4355,10 @@
         <v>42</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G21" s="12"/>
       <c r="H21" s="12">
@@ -4380,10 +4377,10 @@
         <v>43</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G22" s="12"/>
       <c r="H22" s="12">
@@ -4402,17 +4399,17 @@
         <v>44</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G23" s="12"/>
       <c r="H23" s="12">
         <v>1400000</v>
       </c>
       <c r="I23" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>19</v>
@@ -4426,10 +4423,10 @@
         <v>45</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G24" s="12"/>
       <c r="H24" s="12">
@@ -4448,10 +4445,10 @@
         <v>45</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="12">
@@ -4470,10 +4467,10 @@
         <v>46</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G26" s="12">
         <v>480000</v>
@@ -4494,10 +4491,10 @@
         <v>47</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G27" s="12"/>
       <c r="H27" s="12">
@@ -4516,10 +4513,10 @@
         <v>48</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G28" s="12"/>
       <c r="H28" s="12">
@@ -4538,10 +4535,10 @@
         <v>49</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G29" s="12"/>
       <c r="H29" s="12">
@@ -4560,10 +4557,10 @@
         <v>50</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G30" s="12"/>
       <c r="H30" s="12">
@@ -4582,10 +4579,10 @@
         <v>51</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G31" s="12"/>
       <c r="H31" s="12">
@@ -4604,10 +4601,10 @@
         <v>52</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G32" s="12"/>
       <c r="H32" s="12">
@@ -4626,10 +4623,10 @@
         <v>53</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G33" s="12"/>
       <c r="H33" s="12">
@@ -4648,10 +4645,10 @@
         <v>54</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G34" s="12">
         <v>90000</v>
@@ -4669,13 +4666,13 @@
         <v>323</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G35" s="12"/>
       <c r="H35" s="12">
@@ -4694,10 +4691,10 @@
         <v>55</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G36" s="12"/>
       <c r="H36" s="12">
@@ -4716,10 +4713,10 @@
         <v>56</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G37" s="12"/>
       <c r="H37" s="12">
@@ -4738,10 +4735,10 @@
         <v>57</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G38" s="12"/>
       <c r="H38" s="12">
@@ -4760,10 +4757,10 @@
         <v>58</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G39" s="12"/>
       <c r="H39" s="12">
@@ -4782,10 +4779,10 @@
         <v>59</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G40" s="12"/>
       <c r="H40" s="12">
@@ -4804,10 +4801,10 @@
         <v>60</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G41" s="12"/>
       <c r="H41" s="12">
@@ -4826,10 +4823,10 @@
         <v>61</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G42" s="12"/>
       <c r="H42" s="12">
@@ -4848,10 +4845,10 @@
         <v>62</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G43" s="12"/>
       <c r="H43" s="12">
@@ -4870,10 +4867,10 @@
         <v>2703900</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G44" s="12"/>
       <c r="H44" s="12">
@@ -4892,10 +4889,10 @@
         <v>2703900</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G45" s="12"/>
       <c r="H45" s="12">
@@ -4914,10 +4911,10 @@
         <v>63</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G46" s="12"/>
       <c r="H46" s="12">
@@ -4933,20 +4930,20 @@
         <v>24152333903</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G47" s="12"/>
       <c r="H47" s="12">
         <v>50000</v>
       </c>
       <c r="I47" s="12" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>19</v>
@@ -4960,10 +4957,10 @@
         <v>64</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G48" s="12"/>
       <c r="H48" s="12">
@@ -4982,10 +4979,10 @@
         <v>65</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G49" s="12"/>
       <c r="H49" s="12">
@@ -5004,10 +5001,10 @@
         <v>66</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G50" s="12"/>
       <c r="H50" s="12">
@@ -5026,10 +5023,10 @@
         <v>52</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G51" s="12"/>
       <c r="H51" s="12">
@@ -5048,10 +5045,10 @@
         <v>67</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G52" s="12"/>
       <c r="H52" s="12">
@@ -5070,10 +5067,10 @@
         <v>68</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G53" s="12"/>
       <c r="H53" s="12">
@@ -5092,17 +5089,17 @@
         <v>34</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G54" s="12"/>
       <c r="H54" s="12">
         <v>510000</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>19</v>
@@ -5116,10 +5113,10 @@
         <v>69</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G55" s="12"/>
       <c r="H55" s="12">
@@ -5138,10 +5135,10 @@
         <v>70</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G56" s="12"/>
       <c r="H56" s="12">
@@ -5160,10 +5157,10 @@
         <v>71</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G57" s="12"/>
       <c r="H57" s="12">
@@ -5182,10 +5179,10 @@
         <v>71</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G58" s="12"/>
       <c r="H58" s="12">
@@ -5204,10 +5201,10 @@
         <v>72</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G59" s="12"/>
       <c r="H59" s="12">
@@ -5226,10 +5223,10 @@
         <v>73</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G60" s="12"/>
       <c r="H60" s="12">
@@ -5248,10 +5245,10 @@
         <v>74</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G61" s="12"/>
       <c r="H61" s="12">
@@ -5270,10 +5267,10 @@
         <v>75</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G62" s="12"/>
       <c r="H62" s="12">
@@ -5292,10 +5289,10 @@
         <v>76</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G63" s="12">
         <v>14500</v>
@@ -5316,10 +5313,10 @@
         <v>77</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G64" s="12">
         <v>105000</v>
@@ -5328,7 +5325,7 @@
         <v>220000</v>
       </c>
       <c r="I64" s="12" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J64" s="3" t="s">
         <v>19</v>
@@ -5342,10 +5339,10 @@
         <v>78</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G65" s="12">
         <v>105000</v>
@@ -5354,7 +5351,7 @@
         <v>200000</v>
       </c>
       <c r="I65" s="12" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>19</v>
@@ -5368,10 +5365,10 @@
         <v>79</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G66" s="12">
         <v>53000</v>
@@ -5392,10 +5389,10 @@
         <v>80</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G67" s="12">
         <v>12000</v>
@@ -5404,7 +5401,7 @@
         <v>20000</v>
       </c>
       <c r="I67" s="12" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>19</v>
@@ -5418,10 +5415,10 @@
         <v>81</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G68" s="12">
         <v>10000</v>
@@ -5442,10 +5439,10 @@
         <v>82</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G69" s="12">
         <v>13000</v>
@@ -5454,7 +5451,7 @@
         <v>35000</v>
       </c>
       <c r="I69" s="12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J69" s="3" t="s">
         <v>19</v>
@@ -5468,10 +5465,10 @@
         <v>83</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G70" s="12"/>
       <c r="H70" s="12">
@@ -5490,10 +5487,10 @@
         <v>84</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G71" s="12">
         <v>53000</v>
@@ -5502,7 +5499,7 @@
         <v>130000</v>
       </c>
       <c r="I71" s="12" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="J71" s="3" t="s">
         <v>19</v>
@@ -5516,10 +5513,10 @@
         <v>85</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G72" s="12"/>
       <c r="H72" s="12">
@@ -5538,15 +5535,15 @@
         <v>86</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G73" s="12"/>
       <c r="H73" s="12"/>
       <c r="I73" s="12" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="J73" s="3" t="s">
         <v>19</v>
@@ -5560,15 +5557,15 @@
         <v>87</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G74" s="12"/>
       <c r="H74" s="12"/>
       <c r="I74" s="12" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="J74" s="3" t="s">
         <v>19</v>
@@ -5582,10 +5579,10 @@
         <v>88</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G75" s="12">
         <v>70000</v>
@@ -5603,13 +5600,13 @@
         <v>335</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G76" s="12"/>
       <c r="H76" s="12">
@@ -5628,10 +5625,10 @@
         <v>89</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G77" s="12">
         <v>9000</v>
@@ -5652,10 +5649,10 @@
         <v>90</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G78" s="12">
         <v>85000</v>
@@ -5676,10 +5673,10 @@
         <v>91</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G79" s="12">
         <v>85000</v>
@@ -5700,10 +5697,10 @@
         <v>92</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G80" s="12">
         <v>45000</v>
@@ -5712,7 +5709,7 @@
         <v>250000</v>
       </c>
       <c r="I80" s="12" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="J80" s="3" t="s">
         <v>19</v>
@@ -5726,10 +5723,10 @@
         <v>93</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G81" s="12">
         <v>40000</v>
@@ -5750,10 +5747,10 @@
         <v>94</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G82" s="12">
         <v>25000</v>
@@ -5774,10 +5771,10 @@
         <v>95</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G83" s="12">
         <v>16000</v>
@@ -5798,10 +5795,10 @@
         <v>96</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G84" s="12">
         <v>8500</v>
@@ -5810,7 +5807,7 @@
         <v>10000</v>
       </c>
       <c r="I84" s="12" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="J84" s="3" t="s">
         <v>19</v>
@@ -5824,10 +5821,10 @@
         <v>97</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G85" s="12">
         <v>5500</v>
@@ -5848,10 +5845,10 @@
         <v>98</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G86" s="12">
         <v>13000</v>
@@ -5872,10 +5869,10 @@
         <v>99</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G87" s="12">
         <v>160000</v>
@@ -5896,10 +5893,10 @@
         <v>100</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G88" s="12">
         <v>250000</v>
@@ -5920,10 +5917,10 @@
         <v>101</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G89" s="12">
         <v>160000</v>
@@ -5944,10 +5941,10 @@
         <v>102</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G90" s="12">
         <v>4500</v>
@@ -5956,7 +5953,7 @@
         <v>15000</v>
       </c>
       <c r="I90" s="12" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J90" s="3" t="s">
         <v>19</v>
@@ -5970,10 +5967,10 @@
         <v>102</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G91" s="12">
         <v>3300</v>
@@ -5982,7 +5979,7 @@
         <v>15000</v>
       </c>
       <c r="I91" s="12" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>19</v>
@@ -5996,10 +5993,10 @@
         <v>103</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G92" s="12">
         <v>33000</v>
@@ -6008,7 +6005,7 @@
         <v>50000</v>
       </c>
       <c r="I92" s="12" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="J92" s="3" t="s">
         <v>19</v>
@@ -6022,10 +6019,10 @@
         <v>104</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G93" s="12"/>
       <c r="H93" s="12">
@@ -6044,17 +6041,17 @@
         <v>105</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G94" s="12"/>
       <c r="H94" s="12">
         <v>1200000</v>
       </c>
       <c r="I94" s="12" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>19</v>
@@ -6068,10 +6065,10 @@
         <v>106</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G95" s="12">
         <v>0</v>
@@ -6080,7 +6077,7 @@
         <v>250000</v>
       </c>
       <c r="I95" s="12" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="J95" s="3" t="s">
         <v>19</v>
@@ -6094,10 +6091,10 @@
         <v>107</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G96" s="12">
         <v>150000</v>
@@ -6118,10 +6115,10 @@
         <v>108</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G97" s="12">
         <v>11200</v>
@@ -6130,7 +6127,7 @@
         <v>25000</v>
       </c>
       <c r="I97" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="J97" s="3" t="s">
         <v>19</v>
@@ -6144,10 +6141,10 @@
         <v>108</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G98" s="12">
         <v>45000</v>
@@ -6156,7 +6153,7 @@
         <v>65000</v>
       </c>
       <c r="I98" s="12" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="J98" s="3" t="s">
         <v>19</v>
@@ -6170,10 +6167,10 @@
         <v>109</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G99" s="12"/>
       <c r="H99" s="12">
@@ -6192,17 +6189,17 @@
         <v>110</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G100" s="12"/>
       <c r="H100" s="12">
         <v>450000</v>
       </c>
       <c r="I100" s="12" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>19</v>
@@ -6216,10 +6213,10 @@
         <v>111</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G101" s="12">
         <v>340000</v>
@@ -6228,7 +6225,7 @@
         <v>550000</v>
       </c>
       <c r="I101" s="12" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>19</v>
@@ -6242,17 +6239,17 @@
         <v>110</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G102" s="12"/>
       <c r="H102" s="12">
         <v>400000</v>
       </c>
       <c r="I102" s="12" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="J102" s="3" t="s">
         <v>19</v>
@@ -6263,20 +6260,20 @@
         <v>24152333907</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G103" s="12"/>
       <c r="H103" s="12">
         <v>50000</v>
       </c>
       <c r="I103" s="12" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="J103" s="3" t="s">
         <v>19</v>
@@ -6290,10 +6287,10 @@
         <v>112</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G104" s="12"/>
       <c r="H104" s="12">
@@ -6312,10 +6309,10 @@
         <v>113</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G105" s="12">
         <v>150000</v>
@@ -6324,7 +6321,7 @@
         <v>210000</v>
       </c>
       <c r="I105" s="12" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="J105" s="3" t="s">
         <v>19</v>
@@ -6338,10 +6335,10 @@
         <v>34</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G106" s="12"/>
       <c r="H106" s="12">
@@ -6360,10 +6357,10 @@
         <v>114</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G107" s="12"/>
       <c r="H107" s="12">
@@ -6382,10 +6379,10 @@
         <v>115</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G108" s="12">
         <v>0</v>
@@ -6394,7 +6391,7 @@
         <v>10000</v>
       </c>
       <c r="I108" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="J108" s="3" t="s">
         <v>19</v>
@@ -6408,10 +6405,10 @@
         <v>116</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G109" s="12"/>
       <c r="H109" s="12">
@@ -6430,10 +6427,10 @@
         <v>117</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G110" s="12">
         <v>8000</v>
@@ -6456,10 +6453,10 @@
         <v>118</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G111" s="12">
         <v>8000</v>
@@ -6468,7 +6465,7 @@
         <v>15000</v>
       </c>
       <c r="I111" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="J111" s="3" t="s">
         <v>19</v>
@@ -6482,10 +6479,10 @@
         <v>119</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G112" s="12"/>
       <c r="H112" s="12">
@@ -6504,10 +6501,10 @@
         <v>120</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G113" s="12"/>
       <c r="H113" s="12">
@@ -6526,10 +6523,10 @@
         <v>121</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G114" s="12"/>
       <c r="H114" s="12">
@@ -6548,10 +6545,10 @@
         <v>122</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G115" s="12">
         <v>400000</v>
@@ -6560,7 +6557,7 @@
         <v>1200000</v>
       </c>
       <c r="I115" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="J115" s="3" t="s">
         <v>19</v>
@@ -6574,10 +6571,10 @@
         <v>123</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G116" s="12">
         <v>380000</v>
@@ -6598,10 +6595,10 @@
         <v>34</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G117" s="12"/>
       <c r="H117" s="12">
@@ -6620,10 +6617,10 @@
         <v>124</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G118" s="12">
         <v>120000</v>
@@ -6644,10 +6641,10 @@
         <v>125</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G119" s="12"/>
       <c r="H119" s="12">
@@ -6666,10 +6663,10 @@
         <v>126</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G120" s="12"/>
       <c r="H120" s="12">
@@ -6688,10 +6685,10 @@
         <v>127</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G121" s="12"/>
       <c r="H121" s="12">
@@ -6710,10 +6707,10 @@
         <v>128</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G122" s="12"/>
       <c r="H122" s="12">
@@ -6732,10 +6729,10 @@
         <v>129</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G123" s="12"/>
       <c r="H123" s="12">
@@ -6754,10 +6751,10 @@
         <v>45</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G124" s="12"/>
       <c r="H124" s="12">
@@ -6776,10 +6773,10 @@
         <v>130</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G125" s="12"/>
       <c r="H125" s="12">
@@ -6798,10 +6795,10 @@
         <v>131</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G126" s="12"/>
       <c r="H126" s="12">
@@ -6820,10 +6817,10 @@
         <v>132</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G127" s="12"/>
       <c r="H127" s="12">
@@ -6842,10 +6839,10 @@
         <v>133</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G128" s="12"/>
       <c r="H128" s="12">
@@ -6864,10 +6861,10 @@
         <v>134</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G129" s="12"/>
       <c r="H129" s="12">
@@ -6886,17 +6883,17 @@
         <v>135</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G130" s="12"/>
       <c r="H130" s="11" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I130" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="J130" s="3" t="s">
         <v>19</v>
@@ -6910,10 +6907,10 @@
         <v>136</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G131" s="12">
         <v>14500</v>
@@ -6934,10 +6931,10 @@
         <v>137</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G132" s="12">
         <v>14500</v>
@@ -6958,10 +6955,10 @@
         <v>138</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G133" s="12"/>
       <c r="H133" s="12">
@@ -6980,10 +6977,10 @@
         <v>139</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G134" s="12"/>
       <c r="H134" s="12">
@@ -7002,10 +6999,10 @@
         <v>140</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G135" s="12">
         <v>440000</v>
@@ -7026,10 +7023,10 @@
         <v>141</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G136" s="12">
         <v>35000</v>
@@ -7050,10 +7047,10 @@
         <v>134</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G137" s="12"/>
       <c r="H137" s="12"/>
@@ -7070,10 +7067,10 @@
         <v>142</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G138" s="12"/>
       <c r="H138" s="12">
@@ -7092,10 +7089,10 @@
         <v>143</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G139" s="12"/>
       <c r="H139" s="12">
@@ -7114,10 +7111,10 @@
         <v>144</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G140" s="12"/>
       <c r="H140" s="12">
@@ -7136,10 +7133,10 @@
         <v>145</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G141" s="12"/>
       <c r="H141" s="12">
@@ -7158,10 +7155,10 @@
         <v>146</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G142" s="12">
         <v>940000</v>
@@ -7170,7 +7167,7 @@
         <v>990000</v>
       </c>
       <c r="I142" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="J142" s="3" t="s">
         <v>19</v>
@@ -7184,10 +7181,10 @@
         <v>147</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G143" s="12"/>
       <c r="H143" s="12">
@@ -7206,10 +7203,10 @@
         <v>148</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G144" s="12"/>
       <c r="H144" s="12">
@@ -7228,10 +7225,10 @@
         <v>34</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G145" s="12"/>
       <c r="H145" s="12">
@@ -7250,10 +7247,10 @@
         <v>149</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G146" s="12">
         <v>250000</v>
@@ -7274,10 +7271,10 @@
         <v>150</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G147" s="12"/>
       <c r="H147" s="12">
@@ -7296,10 +7293,10 @@
         <v>151</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G148" s="12"/>
       <c r="H148" s="12">
@@ -7318,10 +7315,10 @@
         <v>152</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G149" s="12"/>
       <c r="H149" s="12">
@@ -7340,10 +7337,10 @@
         <v>153</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G150" s="12">
         <v>600000</v>
@@ -7364,10 +7361,10 @@
         <v>154</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G151" s="12">
         <v>45000</v>
@@ -7388,10 +7385,10 @@
         <v>155</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G152" s="12">
         <v>65000</v>
@@ -7400,7 +7397,7 @@
         <v>90000</v>
       </c>
       <c r="I152" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J152" s="3" t="s">
         <v>19</v>
@@ -7414,10 +7411,10 @@
         <v>156</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G153" s="12">
         <v>155000</v>
@@ -7438,10 +7435,10 @@
         <v>157</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G154" s="12">
         <v>260000</v>
@@ -7462,10 +7459,10 @@
         <v>34</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G155" s="12"/>
       <c r="H155" s="12">
@@ -7484,10 +7481,10 @@
         <v>158</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G156" s="12"/>
       <c r="H156" s="12">
@@ -7506,10 +7503,10 @@
         <v>159</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G157" s="12"/>
       <c r="H157" s="12">
@@ -7528,10 +7525,10 @@
         <v>160</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G158" s="12"/>
       <c r="H158" s="12">
@@ -7550,10 +7547,10 @@
         <v>34</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G159" s="12">
         <v>448000</v>
@@ -7574,10 +7571,10 @@
         <v>161</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G160" s="12">
         <v>900000</v>
@@ -7598,10 +7595,10 @@
         <v>162</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G161" s="12"/>
       <c r="H161" s="12">
@@ -7620,10 +7617,10 @@
         <v>163</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G162" s="12">
         <v>76000</v>
@@ -7644,10 +7641,10 @@
         <v>164</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G163" s="12"/>
       <c r="H163" s="12">
@@ -7666,10 +7663,10 @@
         <v>165</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G164" s="12">
         <v>55000</v>
@@ -7690,17 +7687,17 @@
         <v>166</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G165" s="12"/>
       <c r="H165" s="12">
         <v>450000</v>
       </c>
       <c r="I165" s="12" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="J165" s="3" t="s">
         <v>19</v>
@@ -7714,10 +7711,10 @@
         <v>167</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G166" s="12"/>
       <c r="H166" s="12">
@@ -7736,10 +7733,10 @@
         <v>168</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G167" s="12">
         <v>520000</v>
@@ -7760,10 +7757,10 @@
         <v>169</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G168" s="12"/>
       <c r="H168" s="12">
@@ -7782,10 +7779,10 @@
         <v>170</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G169" s="12"/>
       <c r="H169" s="12">
@@ -7804,10 +7801,10 @@
         <v>171</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G170" s="12">
         <v>627000</v>
@@ -7828,10 +7825,10 @@
         <v>172</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G171" s="12">
         <v>69000</v>
@@ -7852,10 +7849,10 @@
         <v>173</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G172" s="12"/>
       <c r="H172" s="12">
@@ -7874,10 +7871,10 @@
         <v>174</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G173" s="12"/>
       <c r="H173" s="12">
@@ -7896,10 +7893,10 @@
         <v>175</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G174" s="12"/>
       <c r="H174" s="12">
@@ -7918,10 +7915,10 @@
         <v>176</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G175" s="12"/>
       <c r="H175" s="12">
@@ -7940,10 +7937,10 @@
         <v>177</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G176" s="12"/>
       <c r="H176" s="12">
@@ -7962,10 +7959,10 @@
         <v>178</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G177" s="12">
         <v>1250000</v>
@@ -7986,10 +7983,10 @@
         <v>179</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G178" s="12">
         <v>1250000</v>
@@ -8010,10 +8007,10 @@
         <v>180</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G179" s="12"/>
       <c r="H179" s="12">
@@ -8032,10 +8029,10 @@
         <v>181</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G180" s="12"/>
       <c r="H180" s="12">
@@ -8054,10 +8051,10 @@
         <v>182</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G181" s="12"/>
       <c r="H181" s="12">
@@ -8076,10 +8073,10 @@
         <v>183</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G182" s="12"/>
       <c r="H182" s="12">
@@ -8098,10 +8095,10 @@
         <v>184</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G183" s="12"/>
       <c r="H183" s="12">
@@ -8120,10 +8117,10 @@
         <v>185</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G184" s="12">
         <v>150000</v>
@@ -8132,7 +8129,7 @@
         <v>300000</v>
       </c>
       <c r="I184" s="12" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="J184" s="3" t="s">
         <v>19</v>
@@ -8146,10 +8143,10 @@
         <v>186</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G185" s="12">
         <v>150000</v>
@@ -8158,7 +8155,7 @@
         <v>300000</v>
       </c>
       <c r="I185" s="12" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="J185" s="3" t="s">
         <v>19</v>
@@ -8172,10 +8169,10 @@
         <v>187</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G186" s="12">
         <v>150000</v>
@@ -8196,10 +8193,10 @@
         <v>188</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G187" s="12">
         <v>67000</v>
@@ -8220,10 +8217,10 @@
         <v>189</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G188" s="12">
         <v>13000</v>
@@ -8244,10 +8241,10 @@
         <v>190</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G189" s="12"/>
       <c r="H189" s="12"/>
@@ -8264,10 +8261,10 @@
         <v>191</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G190" s="12"/>
       <c r="H190" s="12"/>
@@ -8284,10 +8281,10 @@
         <v>192</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G191" s="12"/>
       <c r="H191" s="12">
@@ -8306,10 +8303,10 @@
         <v>193</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G192" s="12"/>
       <c r="H192" s="12">
@@ -8328,10 +8325,10 @@
         <v>194</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G193" s="12"/>
       <c r="H193" s="12">
@@ -8350,10 +8347,10 @@
         <v>195</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G194" s="12"/>
       <c r="H194" s="12">
@@ -8372,10 +8369,10 @@
         <v>196</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G195" s="12"/>
       <c r="H195" s="12">
@@ -8394,10 +8391,10 @@
         <v>197</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G196" s="12"/>
       <c r="H196" s="12">
@@ -8416,10 +8413,10 @@
         <v>198</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G197" s="12">
         <v>140000</v>
@@ -8440,10 +8437,10 @@
         <v>199</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G198" s="12"/>
       <c r="H198" s="12">
@@ -8462,10 +8459,10 @@
         <v>200</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G199" s="12"/>
       <c r="H199" s="12">
@@ -8484,10 +8481,10 @@
         <v>201</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G200" s="12"/>
       <c r="H200" s="12">
@@ -8506,10 +8503,10 @@
         <v>201</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G201" s="12"/>
       <c r="H201" s="12"/>
@@ -8526,10 +8523,10 @@
         <v>202</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G202" s="12"/>
       <c r="H202" s="12">
@@ -8548,10 +8545,10 @@
         <v>170</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G203" s="12"/>
       <c r="H203" s="12">
@@ -8570,10 +8567,10 @@
         <v>203</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G204" s="12"/>
       <c r="H204" s="12">
@@ -8592,14 +8589,14 @@
         <v>204</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G205" s="12"/>
       <c r="H205" s="11" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I205" s="12"/>
       <c r="J205" s="3" t="s">
@@ -8614,10 +8611,10 @@
         <v>205</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G206" s="12"/>
       <c r="H206" s="12"/>
@@ -8634,15 +8631,15 @@
         <v>206</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G207" s="12"/>
       <c r="H207" s="12"/>
       <c r="I207" s="12" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J207" s="3" t="s">
         <v>19</v>
@@ -8656,10 +8653,10 @@
         <v>207</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G208" s="12"/>
       <c r="H208" s="12">
@@ -8678,10 +8675,10 @@
         <v>208</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G209" s="12"/>
       <c r="H209" s="12">
@@ -8700,15 +8697,15 @@
         <v>209</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G210" s="12"/>
       <c r="H210" s="12"/>
       <c r="I210" s="12" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="J210" s="3" t="s">
         <v>19</v>
@@ -8722,10 +8719,10 @@
         <v>210</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G211" s="12"/>
       <c r="H211" s="12">
@@ -8744,10 +8741,10 @@
         <v>211</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G212" s="12"/>
       <c r="H212" s="12">
@@ -8766,10 +8763,10 @@
         <v>212</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G213" s="12"/>
       <c r="H213" s="12">
@@ -8788,10 +8785,10 @@
         <v>213</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G214" s="12"/>
       <c r="H214" s="12">
@@ -8810,10 +8807,10 @@
         <v>214</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G215" s="12"/>
       <c r="H215" s="12"/>
@@ -8830,10 +8827,10 @@
         <v>215</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G216" s="12"/>
       <c r="H216" s="12">
@@ -8852,10 +8849,10 @@
         <v>216</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G217" s="12"/>
       <c r="H217" s="12">
@@ -8874,10 +8871,10 @@
         <v>217</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G218" s="12"/>
       <c r="H218" s="12">
@@ -8896,10 +8893,10 @@
         <v>218</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G219" s="12">
         <v>160000</v>
@@ -8920,10 +8917,10 @@
         <v>219</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G220" s="12">
         <v>110000</v>
@@ -8944,10 +8941,10 @@
         <v>217</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G221" s="12"/>
       <c r="H221" s="12">
@@ -8966,10 +8963,10 @@
         <v>220</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F222" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G222" s="12"/>
       <c r="H222" s="12">
@@ -8988,10 +8985,10 @@
         <v>221</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G223" s="12">
         <v>15000</v>
@@ -9012,10 +9009,10 @@
         <v>222</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G224" s="12"/>
       <c r="H224" s="12">
@@ -9034,10 +9031,10 @@
         <v>223</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F225" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G225" s="12"/>
       <c r="H225" s="12">
@@ -9056,10 +9053,10 @@
         <v>224</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G226" s="12"/>
       <c r="H226" s="12">
@@ -9078,10 +9075,10 @@
         <v>225</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G227" s="12"/>
       <c r="H227" s="12"/>
@@ -9098,10 +9095,10 @@
         <v>226</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G228" s="12"/>
       <c r="H228" s="12">
@@ -9120,17 +9117,17 @@
         <v>227</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G229" s="12"/>
       <c r="H229" s="12">
         <v>1000000</v>
       </c>
       <c r="I229" s="12" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J229" s="3" t="s">
         <v>19</v>
@@ -9144,17 +9141,17 @@
         <v>228</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G230" s="12"/>
       <c r="H230" s="12">
         <v>200000</v>
       </c>
       <c r="I230" s="12" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J230" s="3" t="s">
         <v>19</v>
@@ -9168,10 +9165,10 @@
         <v>229</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G231" s="12">
         <v>200000</v>
@@ -9192,10 +9189,10 @@
         <v>230</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G232" s="12"/>
       <c r="H232" s="12">
@@ -9214,10 +9211,10 @@
         <v>231</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F233" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G233" s="12"/>
       <c r="H233" s="12">
@@ -9236,10 +9233,10 @@
         <v>200</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F234" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G234" s="12"/>
       <c r="H234" s="12">
@@ -9258,10 +9255,10 @@
         <v>232</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G235" s="12"/>
       <c r="H235" s="12">
@@ -9280,10 +9277,10 @@
         <v>233</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G236" s="12"/>
       <c r="H236" s="12">
@@ -9302,10 +9299,10 @@
         <v>234</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G237" s="12">
         <v>85000</v>
@@ -9326,10 +9323,10 @@
         <v>200</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G238" s="12"/>
       <c r="H238" s="12">
@@ -9348,10 +9345,10 @@
         <v>235</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G239" s="12"/>
       <c r="H239" s="12">
@@ -9370,10 +9367,10 @@
         <v>170</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G240" s="12"/>
       <c r="H240" s="12"/>
@@ -9390,10 +9387,10 @@
         <v>201</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G241" s="12"/>
       <c r="H241" s="12">
@@ -9412,10 +9409,10 @@
         <v>236</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F242" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G242" s="12"/>
       <c r="H242" s="12">
@@ -9434,10 +9431,10 @@
         <v>45</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F243" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G243" s="12"/>
       <c r="H243" s="12">
@@ -9456,10 +9453,10 @@
         <v>237</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F244" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G244" s="12"/>
       <c r="H244" s="12">
@@ -9478,10 +9475,10 @@
         <v>238</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G245" s="12"/>
       <c r="H245" s="12"/>
@@ -9498,10 +9495,10 @@
         <v>239</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F246" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G246" s="12"/>
       <c r="H246" s="12"/>
@@ -9518,10 +9515,10 @@
         <v>105</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F247" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G247" s="12"/>
       <c r="H247" s="12">
@@ -9540,10 +9537,10 @@
         <v>240</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F248" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G248" s="12"/>
       <c r="H248" s="12"/>
@@ -9560,10 +9557,10 @@
         <v>241</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F249" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G249" s="12">
         <v>180000</v>
@@ -9584,10 +9581,10 @@
         <v>242</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F250" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G250" s="12"/>
       <c r="H250" s="12">
@@ -9606,10 +9603,10 @@
         <v>243</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F251" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G251" s="12"/>
       <c r="H251" s="12">
@@ -9628,10 +9625,10 @@
         <v>244</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F252" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G252" s="12"/>
       <c r="H252" s="12">
@@ -9650,10 +9647,10 @@
         <v>245</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F253" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G253" s="12"/>
       <c r="H253" s="12">
@@ -9672,10 +9669,10 @@
         <v>246</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F254" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G254" s="12"/>
       <c r="H254" s="12">
@@ -9694,10 +9691,10 @@
         <v>247</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F255" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G255" s="12"/>
       <c r="H255" s="12">
@@ -9716,10 +9713,10 @@
         <v>248</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G256" s="12"/>
       <c r="H256" s="12">
@@ -9738,10 +9735,10 @@
         <v>249</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G257" s="12">
         <v>40000</v>
@@ -9762,10 +9759,10 @@
         <v>250</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F258" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G258" s="12"/>
       <c r="H258" s="12">
@@ -9784,10 +9781,10 @@
         <v>251</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F259" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G259" s="12"/>
       <c r="H259" s="12"/>
@@ -9804,10 +9801,10 @@
         <v>252</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F260" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G260" s="12"/>
       <c r="H260" s="12"/>
@@ -9824,10 +9821,10 @@
         <v>253</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F261" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G261" s="12"/>
       <c r="H261" s="12">
@@ -9846,10 +9843,10 @@
         <v>254</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F262" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G262" s="12"/>
       <c r="H262" s="12">
@@ -9868,10 +9865,10 @@
         <v>255</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F263" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G263" s="12"/>
       <c r="H263" s="12">
@@ -9890,10 +9887,10 @@
         <v>256</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G264" s="12">
         <v>110000</v>
@@ -9914,10 +9911,10 @@
         <v>257</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G265" s="12"/>
       <c r="H265" s="12">
@@ -9936,10 +9933,10 @@
         <v>258</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F266" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G266" s="12"/>
       <c r="H266" s="12">
@@ -9958,10 +9955,10 @@
         <v>259</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G267" s="12"/>
       <c r="H267" s="12">
@@ -9980,10 +9977,10 @@
         <v>260</v>
       </c>
       <c r="E268" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F268" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G268" s="12"/>
       <c r="H268" s="12">
@@ -10002,10 +9999,10 @@
         <v>261</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G269" s="12"/>
       <c r="H269" s="12">
@@ -10024,10 +10021,10 @@
         <v>262</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F270" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G270" s="12"/>
       <c r="H270" s="12">
@@ -10046,10 +10043,10 @@
         <v>263</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G271" s="12"/>
       <c r="H271" s="12">
@@ -10068,10 +10065,10 @@
         <v>264</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G272" s="12"/>
       <c r="H272" s="12">
@@ -10090,10 +10087,10 @@
         <v>265</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G273" s="12"/>
       <c r="H273" s="12">
@@ -10112,10 +10109,10 @@
         <v>266</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G274" s="12"/>
       <c r="H274" s="12">
@@ -10134,10 +10131,10 @@
         <v>261</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F275" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G275" s="12"/>
       <c r="H275" s="12">
@@ -10156,10 +10153,10 @@
         <v>267</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G276" s="12"/>
       <c r="H276" s="12">
@@ -10178,10 +10175,10 @@
         <v>268</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F277" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G277" s="12"/>
       <c r="H277" s="12">
@@ -10200,17 +10197,17 @@
         <v>269</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G278" s="12"/>
       <c r="H278" s="12">
         <v>1500000</v>
       </c>
       <c r="I278" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J278" s="3" t="s">
         <v>19</v>
@@ -10224,17 +10221,17 @@
         <v>270</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F279" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G279" s="12"/>
       <c r="H279" s="12">
         <v>10000</v>
       </c>
       <c r="I279" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J279" s="3" t="s">
         <v>19</v>
@@ -10245,13 +10242,13 @@
         <v>450</v>
       </c>
       <c r="B280" s="11" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F280" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G280" s="12">
         <v>25000</v>
@@ -10272,10 +10269,10 @@
         <v>261</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F281" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G281" s="12"/>
       <c r="H281" s="12">
@@ -10294,10 +10291,10 @@
         <v>271</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F282" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G282" s="12"/>
       <c r="H282" s="12">
@@ -10316,10 +10313,10 @@
         <v>271</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F283" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G283" s="12"/>
       <c r="H283" s="12">
@@ -10340,17 +10337,17 @@
         <v>272</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F284" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G284" s="12"/>
       <c r="H284" s="12">
         <v>100000</v>
       </c>
       <c r="I284" s="12" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="J284" s="3" t="s">
         <v>19</v>
@@ -10364,10 +10361,10 @@
         <v>273</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F285" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G285" s="12"/>
       <c r="H285" s="12">
@@ -10386,10 +10383,10 @@
         <v>274</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F286" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G286" s="12"/>
       <c r="H286" s="12">
@@ -10408,10 +10405,10 @@
         <v>275</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F287" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G287" s="12"/>
       <c r="H287" s="12">
@@ -10430,10 +10427,10 @@
         <v>276</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F288" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G288" s="12"/>
       <c r="H288" s="12">
@@ -10452,10 +10449,10 @@
         <v>277</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F289" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G289" s="12"/>
       <c r="H289" s="12">
@@ -10474,10 +10471,10 @@
         <v>278</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F290" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G290" s="12"/>
       <c r="H290" s="12">
@@ -10496,10 +10493,10 @@
         <v>279</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F291" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G291" s="12"/>
       <c r="H291" s="12">
@@ -10518,10 +10515,10 @@
         <v>280</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F292" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G292" s="12"/>
       <c r="H292" s="12">
@@ -10540,10 +10537,10 @@
         <v>281</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G293" s="12"/>
       <c r="H293" s="12">
@@ -10562,10 +10559,10 @@
         <v>282</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F294" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G294" s="12"/>
       <c r="H294" s="12">
@@ -10584,10 +10581,10 @@
         <v>283</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F295" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G295" s="12"/>
       <c r="H295" s="12">
@@ -10606,17 +10603,17 @@
         <v>284</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G296" s="12"/>
       <c r="H296" s="12">
         <v>1500000</v>
       </c>
       <c r="I296" s="12" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="J296" s="3" t="s">
         <v>19</v>
@@ -10630,10 +10627,10 @@
         <v>285</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F297" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G297" s="12"/>
       <c r="H297" s="12">
@@ -10652,10 +10649,10 @@
         <v>286</v>
       </c>
       <c r="E298" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F298" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G298" s="12"/>
       <c r="H298" s="12">
@@ -10674,10 +10671,10 @@
         <v>287</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F299" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G299" s="12"/>
       <c r="H299" s="12">
@@ -10696,10 +10693,10 @@
         <v>288</v>
       </c>
       <c r="E300" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F300" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G300" s="12"/>
       <c r="H300" s="12">
@@ -10718,10 +10715,10 @@
         <v>289</v>
       </c>
       <c r="E301" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F301" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G301" s="12"/>
       <c r="H301" s="12">
@@ -10740,10 +10737,10 @@
         <v>290</v>
       </c>
       <c r="E302" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F302" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G302" s="12"/>
       <c r="H302" s="12">
@@ -10762,10 +10759,10 @@
         <v>291</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F303" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G303" s="12"/>
       <c r="H303" s="12">
@@ -10784,10 +10781,10 @@
         <v>292</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F304" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G304" s="12"/>
       <c r="H304" s="12">
@@ -10808,10 +10805,10 @@
         <v>293</v>
       </c>
       <c r="E305" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F305" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G305" s="12"/>
       <c r="H305" s="12">
@@ -10830,10 +10827,10 @@
         <v>294</v>
       </c>
       <c r="E306" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F306" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G306" s="12"/>
       <c r="H306" s="12">
@@ -10852,10 +10849,10 @@
         <v>295</v>
       </c>
       <c r="E307" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F307" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G307" s="12"/>
       <c r="H307" s="12">
@@ -10874,10 +10871,10 @@
         <v>296</v>
       </c>
       <c r="E308" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F308" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G308" s="12"/>
       <c r="H308" s="12">
@@ -10896,10 +10893,10 @@
         <v>297</v>
       </c>
       <c r="E309" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F309" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G309" s="12"/>
       <c r="H309" s="12">
@@ -10918,10 +10915,10 @@
         <v>298</v>
       </c>
       <c r="E310" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F310" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G310" s="12"/>
       <c r="H310" s="12">
@@ -10940,10 +10937,10 @@
         <v>299</v>
       </c>
       <c r="E311" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F311" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G311" s="12"/>
       <c r="H311" s="12">
@@ -10962,10 +10959,10 @@
         <v>300</v>
       </c>
       <c r="E312" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F312" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G312" s="12"/>
       <c r="H312" s="12">
@@ -10984,17 +10981,17 @@
         <v>301</v>
       </c>
       <c r="E313" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F313" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G313" s="12"/>
       <c r="H313" s="12">
         <v>1000000</v>
       </c>
       <c r="I313" s="12" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J313" s="3" t="s">
         <v>19</v>
@@ -11008,10 +11005,10 @@
         <v>302</v>
       </c>
       <c r="E314" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F314" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G314" s="12"/>
       <c r="H314" s="12">
@@ -11024,16 +11021,16 @@
     </row>
     <row r="315" spans="1:10">
       <c r="A315" s="11" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B315" s="11" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E315" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F315" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G315" s="12"/>
       <c r="H315" s="12">
@@ -11046,16 +11043,16 @@
     </row>
     <row r="316" spans="1:10">
       <c r="A316" s="11" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B316" s="11" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E316" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F316" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G316" s="12"/>
       <c r="H316" s="12">
@@ -11068,16 +11065,16 @@
     </row>
     <row r="317" spans="1:10">
       <c r="A317" s="11" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B317" s="11" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E317" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F317" s="3" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="G317" s="12"/>
       <c r="H317" s="12">
